--- a/03_Outputs/all/03_DS/ds_idx13_saludmental.xlsx
+++ b/03_Outputs/all/03_DS/ds_idx13_saludmental.xlsx
@@ -406,16 +406,16 @@
         <v>1.733284021458048</v>
       </c>
       <c r="D2">
-        <v>0.875074692235435</v>
+        <v>0.8750746922354357</v>
       </c>
       <c r="E2">
-        <v>0.0843886300633661</v>
+        <v>0.08438863006336618</v>
       </c>
       <c r="F2">
-        <v>0.04511509535563572</v>
+        <v>0.04511509535563556</v>
       </c>
       <c r="G2">
-        <v>0.1102266807563243</v>
+        <v>0.1102266807563238</v>
       </c>
     </row>
     <row r="3">
@@ -433,16 +433,16 @@
         <v>7.566282377562165</v>
       </c>
       <c r="D3">
-        <v>2.735712866379851</v>
+        <v>2.735712866379852</v>
       </c>
       <c r="E3">
-        <v>-0.08357852261515625</v>
+        <v>-0.08357852261515684</v>
       </c>
       <c r="F3">
-        <v>-0.1949564705581743</v>
+        <v>-0.1949564705581748</v>
       </c>
       <c r="G3">
-        <v>-0.1819450995889538</v>
+        <v>-0.1819450995889552</v>
       </c>
     </row>
     <row r="4">
@@ -457,19 +457,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>1.767905815200352</v>
+        <v>1.767905815200354</v>
       </c>
       <c r="D4">
-        <v>-6.833295902795034</v>
+        <v>-6.833295902795035</v>
       </c>
       <c r="E4">
-        <v>3.729507885434812</v>
+        <v>3.729507885434808</v>
       </c>
       <c r="F4">
-        <v>-2.79817967923494</v>
+        <v>-2.798179679234941</v>
       </c>
       <c r="G4">
-        <v>-0.7680665924210195</v>
+        <v>-0.7680665924210196</v>
       </c>
     </row>
     <row r="5">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>-0.238761518673269</v>
+        <v>-0.2387615186732678</v>
       </c>
       <c r="D5">
-        <v>-2.998307532178538</v>
+        <v>-2.998307532178536</v>
       </c>
       <c r="E5">
-        <v>2.223971355248794</v>
+        <v>2.22397135524879</v>
       </c>
       <c r="F5">
         <v>-1.741622224594974</v>
       </c>
       <c r="G5">
-        <v>1.544964088813635</v>
+        <v>1.544964088813636</v>
       </c>
     </row>
     <row r="6">
@@ -511,19 +511,19 @@
         </is>
       </c>
       <c r="C6">
-        <v>-3.003694239790364</v>
+        <v>-3.003694239790363</v>
       </c>
       <c r="D6">
-        <v>-0.4074811068910008</v>
+        <v>-0.4074811068910006</v>
       </c>
       <c r="E6">
-        <v>-0.8474752399148326</v>
+        <v>-0.8474752399148319</v>
       </c>
       <c r="F6">
-        <v>0.02509436616570972</v>
+        <v>0.02509436616571094</v>
       </c>
       <c r="G6">
-        <v>0.1304498222595899</v>
+        <v>0.1304498222595905</v>
       </c>
     </row>
     <row r="7">
@@ -538,19 +538,19 @@
         </is>
       </c>
       <c r="C7">
-        <v>-0.573178954812632</v>
+        <v>-0.5731789548126307</v>
       </c>
       <c r="D7">
-        <v>-0.2288841012251574</v>
+        <v>-0.2288841012251568</v>
       </c>
       <c r="E7">
-        <v>-0.5236637144215966</v>
+        <v>-0.5236637144215963</v>
       </c>
       <c r="F7">
-        <v>0.02956937894745609</v>
+        <v>0.0295693789474569</v>
       </c>
       <c r="G7">
-        <v>0.6092832839980817</v>
+        <v>0.6092832839980821</v>
       </c>
     </row>
     <row r="8">
@@ -565,19 +565,19 @@
         </is>
       </c>
       <c r="C8">
-        <v>-0.8761134293981967</v>
+        <v>-0.8761134293981955</v>
       </c>
       <c r="D8">
-        <v>-1.895278070530163</v>
+        <v>-1.895278070530162</v>
       </c>
       <c r="E8">
-        <v>0.4428970863363224</v>
+        <v>0.4428970863363215</v>
       </c>
       <c r="F8">
-        <v>-0.6294587159964292</v>
+        <v>-0.6294587159964288</v>
       </c>
       <c r="G8">
-        <v>0.2875433988702958</v>
+        <v>0.2875433988702961</v>
       </c>
     </row>
     <row r="9">
@@ -592,19 +592,19 @@
         </is>
       </c>
       <c r="C9">
-        <v>1.440350076370978</v>
+        <v>1.440350076370981</v>
       </c>
       <c r="D9">
-        <v>-5.572422253383086</v>
+        <v>-5.572422253383087</v>
       </c>
       <c r="E9">
-        <v>-4.988878314285289</v>
+        <v>-4.98887831428528</v>
       </c>
       <c r="F9">
-        <v>2.217379590120822</v>
+        <v>2.217379590120829</v>
       </c>
       <c r="G9">
-        <v>-0.04386135718375179</v>
+        <v>-0.04386135718375402</v>
       </c>
     </row>
     <row r="10">
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="C10">
-        <v>1.151688117252479</v>
+        <v>1.15168811725248</v>
       </c>
       <c r="D10">
         <v>-1.48081823589302</v>
       </c>
       <c r="E10">
-        <v>-0.3097345402582339</v>
+        <v>-0.3097345402582358</v>
       </c>
       <c r="F10">
-        <v>-1.662755582543383</v>
+        <v>-1.662755582543381</v>
       </c>
       <c r="G10">
-        <v>-0.4811051129799385</v>
+        <v>-0.481105112979939</v>
       </c>
     </row>
     <row r="11">
@@ -646,19 +646,19 @@
         </is>
       </c>
       <c r="C11">
-        <v>-2.408339787020385</v>
+        <v>-2.408339787020383</v>
       </c>
       <c r="D11">
-        <v>0.8433871128892901</v>
+        <v>0.8433871128892905</v>
       </c>
       <c r="E11">
         <v>-1.078456420990181</v>
       </c>
       <c r="F11">
-        <v>-0.2162580982333692</v>
+        <v>-0.2162580982333679</v>
       </c>
       <c r="G11">
-        <v>0.201771909478005</v>
+        <v>0.2017719094780054</v>
       </c>
     </row>
     <row r="12">
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="C12">
-        <v>-2.368512861789541</v>
+        <v>-2.368512861789539</v>
       </c>
       <c r="D12">
         <v>-0.2891121584740772</v>
       </c>
       <c r="E12">
-        <v>0.4015872941226618</v>
+        <v>0.4015872941226624</v>
       </c>
       <c r="F12">
-        <v>0.2964167267798118</v>
+        <v>0.2964167267798112</v>
       </c>
       <c r="G12">
-        <v>-0.02831764581549161</v>
+        <v>-0.02831764581549119</v>
       </c>
     </row>
     <row r="13">
@@ -700,19 +700,19 @@
         </is>
       </c>
       <c r="C13">
-        <v>-0.2447120194050929</v>
+        <v>-0.2447120194050919</v>
       </c>
       <c r="D13">
-        <v>0.6157599961365517</v>
+        <v>0.6157599961365516</v>
       </c>
       <c r="E13">
-        <v>0.4245163699800167</v>
+        <v>0.4245163699800166</v>
       </c>
       <c r="F13">
-        <v>0.3018087653714894</v>
+        <v>0.3018087653714882</v>
       </c>
       <c r="G13">
-        <v>-0.2348152016811354</v>
+        <v>-0.2348152016811352</v>
       </c>
     </row>
     <row r="14">
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="C14">
-        <v>-1.162178101876844</v>
+        <v>-1.162178101876843</v>
       </c>
       <c r="D14">
-        <v>0.7161365410651064</v>
+        <v>0.7161365410651068</v>
       </c>
       <c r="E14">
-        <v>0.08595735780510375</v>
+        <v>0.08595735780510329</v>
       </c>
       <c r="F14">
         <v>-0.2600092663340621</v>
       </c>
       <c r="G14">
-        <v>0.04118144909745387</v>
+        <v>0.04118144909745404</v>
       </c>
     </row>
     <row r="15">
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="C15">
-        <v>-1.912877319786859</v>
+        <v>-1.912877319786857</v>
       </c>
       <c r="D15">
-        <v>1.193718527078645</v>
+        <v>1.193718527078646</v>
       </c>
       <c r="E15">
         <v>0.1920184891448768</v>
       </c>
       <c r="F15">
-        <v>0.1589002992954457</v>
+        <v>0.1589002992954453</v>
       </c>
       <c r="G15">
-        <v>0.1895526743622485</v>
+        <v>0.1895526743622489</v>
       </c>
     </row>
     <row r="16">
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="C16">
-        <v>0.7789524500782045</v>
+        <v>0.7789524500782058</v>
       </c>
       <c r="D16">
-        <v>-0.3871980990841457</v>
+        <v>-0.3871980990841466</v>
       </c>
       <c r="E16">
-        <v>-0.9461088282366071</v>
+        <v>-0.9461088282366099</v>
       </c>
       <c r="F16">
-        <v>-2.184042578973703</v>
+        <v>-2.1840425789737</v>
       </c>
       <c r="G16">
-        <v>-1.605779250773588</v>
+        <v>-1.605779250773587</v>
       </c>
     </row>
     <row r="17">
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C17">
-        <v>-2.345066127203609</v>
+        <v>-2.345066127203607</v>
       </c>
       <c r="D17">
         <v>1.814395580098347</v>
       </c>
       <c r="E17">
-        <v>0.2927346339123804</v>
+        <v>0.2927346339123803</v>
       </c>
       <c r="F17">
-        <v>-0.1463716656292794</v>
+        <v>-0.1463716656292803</v>
       </c>
       <c r="G17">
-        <v>-0.7482453898213434</v>
+        <v>-0.7482453898213439</v>
       </c>
     </row>
     <row r="18">
@@ -835,16 +835,16 @@
         </is>
       </c>
       <c r="C18">
-        <v>0.1204915254782696</v>
+        <v>0.1204915254782704</v>
       </c>
       <c r="D18">
-        <v>0.3145827432791907</v>
+        <v>0.3145827432791914</v>
       </c>
       <c r="E18">
-        <v>0.6634955845684841</v>
+        <v>0.6634955845684832</v>
       </c>
       <c r="F18">
-        <v>-0.3797624920760897</v>
+        <v>-0.3797624920760903</v>
       </c>
       <c r="G18">
         <v>0.2688803355563328</v>
@@ -871,10 +871,10 @@
         <v>0.2581130283022161</v>
       </c>
       <c r="F19">
-        <v>0.06029460726638443</v>
+        <v>0.06029460726638353</v>
       </c>
       <c r="G19">
-        <v>-0.5453404564308295</v>
+        <v>-0.5453404564308297</v>
       </c>
     </row>
     <row r="20">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="C20">
-        <v>0.9823510076529492</v>
+        <v>0.9823510076529496</v>
       </c>
       <c r="D20">
         <v>1.119677452471575</v>
@@ -898,10 +898,10 @@
         <v>0.1801882893092835</v>
       </c>
       <c r="F20">
-        <v>0.0809580739520282</v>
+        <v>0.08095807395202786</v>
       </c>
       <c r="G20">
-        <v>0.1085048268460771</v>
+        <v>0.1085048268460768</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="C21">
-        <v>-3.00688240777579</v>
+        <v>-3.006882407775789</v>
       </c>
       <c r="D21">
         <v>1.614709865292327</v>
       </c>
       <c r="E21">
-        <v>0.2711633306591683</v>
+        <v>0.2711633306591685</v>
       </c>
       <c r="F21">
-        <v>0.1992269348636032</v>
+        <v>0.1992269348636024</v>
       </c>
       <c r="G21">
-        <v>-1.134225128375352</v>
+        <v>-1.134225128375353</v>
       </c>
     </row>
     <row r="22">
@@ -943,19 +943,19 @@
         </is>
       </c>
       <c r="C22">
-        <v>0.4144521774259159</v>
+        <v>0.4144521774259167</v>
       </c>
       <c r="D22">
-        <v>1.453555734427221</v>
+        <v>1.453555734427222</v>
       </c>
       <c r="E22">
-        <v>0.05601131337780228</v>
+        <v>0.05601131337780296</v>
       </c>
       <c r="F22">
-        <v>0.5860075701696766</v>
+        <v>0.5860075701696761</v>
       </c>
       <c r="G22">
-        <v>0.1476683737914482</v>
+        <v>0.1476683737914481</v>
       </c>
     </row>
     <row r="23">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="C23">
-        <v>-1.158036353699153</v>
+        <v>-1.158036353699152</v>
       </c>
       <c r="D23">
-        <v>0.9839698251297089</v>
+        <v>0.9839698251297092</v>
       </c>
       <c r="E23">
-        <v>0.601337824643116</v>
+        <v>0.6013378246431154</v>
       </c>
       <c r="F23">
-        <v>-0.09810629298587181</v>
+        <v>-0.09810629298587269</v>
       </c>
       <c r="G23">
-        <v>-0.2250832303016824</v>
+        <v>-0.2250832303016821</v>
       </c>
     </row>
     <row r="24">
@@ -997,16 +997,16 @@
         </is>
       </c>
       <c r="C24">
-        <v>-0.062784719250363</v>
+        <v>-0.06278471925036191</v>
       </c>
       <c r="D24">
-        <v>-0.9695068738464373</v>
+        <v>-0.9695068738464374</v>
       </c>
       <c r="E24">
-        <v>1.471294997519855</v>
+        <v>1.471294997519854</v>
       </c>
       <c r="F24">
-        <v>-0.4554043081401599</v>
+        <v>-0.4554043081401611</v>
       </c>
       <c r="G24">
         <v>-1.206974215637154</v>
@@ -1024,19 +1024,19 @@
         </is>
       </c>
       <c r="C25">
-        <v>-0.5051182268360489</v>
+        <v>-0.5051182268360473</v>
       </c>
       <c r="D25">
-        <v>-0.9898646065932064</v>
+        <v>-0.9898646065932065</v>
       </c>
       <c r="E25">
-        <v>-0.2808044836154853</v>
+        <v>-0.2808044836154823</v>
       </c>
       <c r="F25">
         <v>1.358106547157736</v>
       </c>
       <c r="G25">
-        <v>0.4002004534224385</v>
+        <v>0.4002004534224382</v>
       </c>
     </row>
     <row r="26">
@@ -1051,19 +1051,19 @@
         </is>
       </c>
       <c r="C26">
-        <v>-2.878845739627918</v>
+        <v>-2.878845739627917</v>
       </c>
       <c r="D26">
-        <v>1.421064237465516</v>
+        <v>1.421064237465517</v>
       </c>
       <c r="E26">
-        <v>0.2676477529444131</v>
+        <v>0.2676477529444125</v>
       </c>
       <c r="F26">
-        <v>-0.1353992504073958</v>
+        <v>-0.1353992504073965</v>
       </c>
       <c r="G26">
-        <v>0.2749167998553099</v>
+        <v>0.2749167998553106</v>
       </c>
     </row>
     <row r="27">
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="C27">
-        <v>-1.792826045746549</v>
+        <v>-1.792826045746548</v>
       </c>
       <c r="D27">
         <v>-1.024709223200337</v>
       </c>
       <c r="E27">
-        <v>-0.4212815344305333</v>
+        <v>-0.42128153443053</v>
       </c>
       <c r="F27">
         <v>1.534185370236844</v>
       </c>
       <c r="G27">
-        <v>0.3513349966529806</v>
+        <v>0.3513349966529804</v>
       </c>
     </row>
     <row r="28">
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="C28">
-        <v>-1.880623443357105</v>
+        <v>-1.880623443357103</v>
       </c>
       <c r="D28">
-        <v>-0.257121546778161</v>
+        <v>-0.2571215467781607</v>
       </c>
       <c r="E28">
-        <v>0.3143796753439563</v>
+        <v>0.3143796753439566</v>
       </c>
       <c r="F28">
-        <v>0.07168519611022685</v>
+        <v>0.0716851961102265</v>
       </c>
       <c r="G28">
-        <v>0.1599394305170759</v>
+        <v>0.1599394305170761</v>
       </c>
     </row>
     <row r="29">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="C29">
-        <v>-0.7320969789531065</v>
+        <v>-0.7320969789531053</v>
       </c>
       <c r="D29">
         <v>-1.68576991226344</v>
       </c>
       <c r="E29">
-        <v>-0.847920657736268</v>
+        <v>-0.8479206577362669</v>
       </c>
       <c r="F29">
-        <v>-0.008613331023158664</v>
+        <v>-0.008613331023157034</v>
       </c>
       <c r="G29">
-        <v>0.5333204154383892</v>
+        <v>0.5333204154383887</v>
       </c>
     </row>
     <row r="30">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="C30">
-        <v>-1.033451603151443</v>
+        <v>-1.033451603151442</v>
       </c>
       <c r="D30">
-        <v>0.1462516312375275</v>
+        <v>0.1462516312375283</v>
       </c>
       <c r="E30">
-        <v>-0.3565092892614684</v>
+        <v>-0.3565092892614675</v>
       </c>
       <c r="F30">
-        <v>0.1534798540059613</v>
+        <v>0.1534798540059618</v>
       </c>
       <c r="G30">
-        <v>0.6666698372815196</v>
+        <v>0.6666698372815193</v>
       </c>
     </row>
     <row r="31">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="C31">
-        <v>-0.2783170975167047</v>
+        <v>-0.2783170975167034</v>
       </c>
       <c r="D31">
-        <v>-3.135101685288022</v>
+        <v>-3.135101685288021</v>
       </c>
       <c r="E31">
-        <v>2.261806310133989</v>
+        <v>2.261806310133985</v>
       </c>
       <c r="F31">
-        <v>-1.784308274030542</v>
+        <v>-1.784308274030543</v>
       </c>
       <c r="G31">
-        <v>1.548108577619365</v>
+        <v>1.548108577619366</v>
       </c>
     </row>
     <row r="32">
@@ -1213,19 +1213,19 @@
         </is>
       </c>
       <c r="C32">
-        <v>3.575659367338678</v>
+        <v>3.575659367338679</v>
       </c>
       <c r="D32">
         <v>-2.195923890639732</v>
       </c>
       <c r="E32">
-        <v>2.220105194069212</v>
+        <v>2.22010519406921</v>
       </c>
       <c r="F32">
-        <v>-1.187539546589693</v>
+        <v>-1.187539546589695</v>
       </c>
       <c r="G32">
-        <v>-0.5570282684354648</v>
+        <v>-0.5570282684354656</v>
       </c>
     </row>
     <row r="33">
@@ -1240,19 +1240,19 @@
         </is>
       </c>
       <c r="C33">
-        <v>-0.6981195073016269</v>
+        <v>-0.6981195073016262</v>
       </c>
       <c r="D33">
         <v>1.34803452708236</v>
       </c>
       <c r="E33">
-        <v>0.1666478710074913</v>
+        <v>0.1666478710074912</v>
       </c>
       <c r="F33">
-        <v>0.04676453545419646</v>
+        <v>0.04676453545419609</v>
       </c>
       <c r="G33">
-        <v>-0.07402825243154608</v>
+        <v>-0.07402825243154625</v>
       </c>
     </row>
     <row r="34">
@@ -1267,19 +1267,19 @@
         </is>
       </c>
       <c r="C34">
-        <v>1.195292621300802</v>
+        <v>1.195292621300803</v>
       </c>
       <c r="D34">
-        <v>0.2482017987322148</v>
+        <v>0.2482017987322152</v>
       </c>
       <c r="E34">
-        <v>-0.4007886491817044</v>
+        <v>-0.4007886491817032</v>
       </c>
       <c r="F34">
-        <v>0.4498344409237995</v>
+        <v>0.4498344409237999</v>
       </c>
       <c r="G34">
-        <v>0.3334444306105805</v>
+        <v>0.3334444306105803</v>
       </c>
     </row>
     <row r="35">
@@ -1294,19 +1294,19 @@
         </is>
       </c>
       <c r="C35">
-        <v>1.131660623371315</v>
+        <v>1.131660623371316</v>
       </c>
       <c r="D35">
-        <v>2.970298620041673</v>
+        <v>2.970298620041674</v>
       </c>
       <c r="E35">
-        <v>0.08459009876347411</v>
+        <v>0.0845900987634737</v>
       </c>
       <c r="F35">
-        <v>0.7934397288774366</v>
+        <v>0.7934397288774355</v>
       </c>
       <c r="G35">
-        <v>0.0199179115782</v>
+        <v>0.01991791157820159</v>
       </c>
     </row>
     <row r="36">
@@ -1321,19 +1321,19 @@
         </is>
       </c>
       <c r="C36">
-        <v>-0.275093267727417</v>
+        <v>-0.2750932677274164</v>
       </c>
       <c r="D36">
         <v>1.479500596839675</v>
       </c>
       <c r="E36">
-        <v>0.2759116250145039</v>
+        <v>0.2759116250145036</v>
       </c>
       <c r="F36">
-        <v>-0.01702811983492682</v>
+        <v>-0.01702811983492739</v>
       </c>
       <c r="G36">
-        <v>0.1831230858649996</v>
+        <v>0.1831230858649994</v>
       </c>
     </row>
     <row r="37">
@@ -1348,19 +1348,19 @@
         </is>
       </c>
       <c r="C37">
-        <v>0.5778795005225076</v>
+        <v>0.5778795005225085</v>
       </c>
       <c r="D37">
-        <v>-0.1014743413849065</v>
+        <v>-0.1014743413849059</v>
       </c>
       <c r="E37">
-        <v>-0.1165443273672501</v>
+        <v>-0.1165443273672503</v>
       </c>
       <c r="F37">
-        <v>-0.4159483733283159</v>
+        <v>-0.4159483733283152</v>
       </c>
       <c r="G37">
-        <v>0.1416650854551573</v>
+        <v>0.141665085455157</v>
       </c>
     </row>
     <row r="38">
@@ -1381,13 +1381,13 @@
         <v>1.49669582967935</v>
       </c>
       <c r="E38">
-        <v>0.4252309958273603</v>
+        <v>0.4252309958273597</v>
       </c>
       <c r="F38">
-        <v>-0.1533401313086686</v>
+        <v>-0.1533401313086696</v>
       </c>
       <c r="G38">
-        <v>0.3980380972552231</v>
+        <v>0.3980380972552225</v>
       </c>
     </row>
     <row r="39">
@@ -1402,19 +1402,19 @@
         </is>
       </c>
       <c r="C39">
-        <v>-0.03793709389981369</v>
+        <v>-0.03793709389981242</v>
       </c>
       <c r="D39">
         <v>-2.202893832898547</v>
       </c>
       <c r="E39">
-        <v>-0.9866979478382175</v>
+        <v>-0.9866979478382177</v>
       </c>
       <c r="F39">
-        <v>-0.7893535373478189</v>
+        <v>-0.7893535373478167</v>
       </c>
       <c r="G39">
-        <v>0.8670444121916276</v>
+        <v>0.867044412191628</v>
       </c>
     </row>
     <row r="40">
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="C40">
-        <v>2.214928606559147</v>
+        <v>2.214928606559148</v>
       </c>
       <c r="D40">
         <v>-2.413269692370438</v>
       </c>
       <c r="E40">
-        <v>0.4005961742145754</v>
+        <v>0.4005961742145769</v>
       </c>
       <c r="F40">
-        <v>0.4833280186393981</v>
+        <v>0.4833280186393982</v>
       </c>
       <c r="G40">
-        <v>1.257722553865147</v>
+        <v>1.257722553865146</v>
       </c>
     </row>
     <row r="41">
@@ -1462,13 +1462,13 @@
         <v>1.039255054990675</v>
       </c>
       <c r="E41">
-        <v>0.2388714323057379</v>
+        <v>0.2388714323057369</v>
       </c>
       <c r="F41">
-        <v>-0.5234383686231966</v>
+        <v>-0.5234383686231968</v>
       </c>
       <c r="G41">
-        <v>-0.4579525614302027</v>
+        <v>-0.4579525614302025</v>
       </c>
     </row>
     <row r="42">
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="C42">
-        <v>-0.261112329166606</v>
+        <v>-0.2611123291666053</v>
       </c>
       <c r="D42">
         <v>1.28885408695712</v>
@@ -1492,10 +1492,10 @@
         <v>0.2348069843002871</v>
       </c>
       <c r="F42">
-        <v>0.08488522857848879</v>
+        <v>0.08488522857848824</v>
       </c>
       <c r="G42">
-        <v>-0.2395254353457366</v>
+        <v>-0.2395254353457367</v>
       </c>
     </row>
     <row r="43">
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="C43">
-        <v>-2.06587806759513</v>
+        <v>-2.065878067595128</v>
       </c>
       <c r="D43">
         <v>-2.054304554363362</v>
       </c>
       <c r="E43">
-        <v>0.387011476342359</v>
+        <v>0.3870114763423579</v>
       </c>
       <c r="F43">
-        <v>-0.8599563062404647</v>
+        <v>-0.8599563062404639</v>
       </c>
       <c r="G43">
-        <v>-0.0737625128158953</v>
+        <v>-0.07376251281589453</v>
       </c>
     </row>
     <row r="44">
@@ -1537,19 +1537,19 @@
         </is>
       </c>
       <c r="C44">
-        <v>1.324868694258504</v>
+        <v>1.324868694258505</v>
       </c>
       <c r="D44">
-        <v>-1.102492817540048</v>
+        <v>-1.102492817540047</v>
       </c>
       <c r="E44">
-        <v>-0.4875518707162819</v>
+        <v>-0.4875518707162813</v>
       </c>
       <c r="F44">
-        <v>-0.1117234059601042</v>
+        <v>-0.1117234059601033</v>
       </c>
       <c r="G44">
-        <v>0.4670681140292443</v>
+        <v>0.4670681140292438</v>
       </c>
     </row>
     <row r="45">
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="C45">
-        <v>-1.272595462722599</v>
+        <v>-1.272595462722597</v>
       </c>
       <c r="D45">
         <v>-2.410073991104445</v>
       </c>
       <c r="E45">
-        <v>-1.089039996105757</v>
+        <v>-1.089039996105751</v>
       </c>
       <c r="F45">
-        <v>2.374388950968784</v>
+        <v>2.374388950968786</v>
       </c>
       <c r="G45">
-        <v>1.028742546876191</v>
+        <v>1.02874254687619</v>
       </c>
     </row>
     <row r="46">
@@ -1591,19 +1591,19 @@
         </is>
       </c>
       <c r="C46">
-        <v>-2.816591825820587</v>
+        <v>-2.816591825820586</v>
       </c>
       <c r="D46">
-        <v>0.9463012908203022</v>
+        <v>0.9463012908203028</v>
       </c>
       <c r="E46">
-        <v>0.1610533491286858</v>
+        <v>0.161053349128686</v>
       </c>
       <c r="F46">
-        <v>0.2421462810514111</v>
+        <v>0.2421462810514107</v>
       </c>
       <c r="G46">
-        <v>0.1927325666703533</v>
+        <v>0.1927325666703537</v>
       </c>
     </row>
     <row r="47">
@@ -1621,16 +1621,16 @@
         <v>2.226580946955032</v>
       </c>
       <c r="D47">
-        <v>0.7022071581291863</v>
+        <v>0.7022071581291861</v>
       </c>
       <c r="E47">
-        <v>-0.1531077666110896</v>
+        <v>-0.1531077666110865</v>
       </c>
       <c r="F47">
-        <v>1.220355563640514</v>
+        <v>1.220355563640513</v>
       </c>
       <c r="G47">
-        <v>-0.7434413252578691</v>
+        <v>-0.7434413252578711</v>
       </c>
     </row>
     <row r="48">
@@ -1645,19 +1645,19 @@
         </is>
       </c>
       <c r="C48">
-        <v>1.898381369047967</v>
+        <v>1.898381369047968</v>
       </c>
       <c r="D48">
-        <v>1.537400599362496</v>
+        <v>1.537400599362497</v>
       </c>
       <c r="E48">
-        <v>0.1998436662786758</v>
+        <v>0.1998436662786757</v>
       </c>
       <c r="F48">
-        <v>0.107485722626919</v>
+        <v>0.1074857226269185</v>
       </c>
       <c r="G48">
-        <v>0.2678927554639866</v>
+        <v>0.2678927554639862</v>
       </c>
     </row>
     <row r="49">
@@ -1672,19 +1672,19 @@
         </is>
       </c>
       <c r="C49">
-        <v>0.3263648583742915</v>
+        <v>0.3263648583742923</v>
       </c>
       <c r="D49">
-        <v>0.6452108467285099</v>
+        <v>0.6452108467285103</v>
       </c>
       <c r="E49">
-        <v>-0.1945504497195378</v>
+        <v>-0.1945504497195369</v>
       </c>
       <c r="F49">
         <v>0.1489582218558469</v>
       </c>
       <c r="G49">
-        <v>-0.1234937334149858</v>
+        <v>-0.1234937334149866</v>
       </c>
     </row>
     <row r="50">
@@ -1699,16 +1699,16 @@
         </is>
       </c>
       <c r="C50">
-        <v>0.4300005845392108</v>
+        <v>0.4300005845392117</v>
       </c>
       <c r="D50">
-        <v>-0.3031130108994067</v>
+        <v>-0.303113010899406</v>
       </c>
       <c r="E50">
-        <v>0.03131386864564813</v>
+        <v>0.03131386864564824</v>
       </c>
       <c r="F50">
-        <v>-0.1322865996033787</v>
+        <v>-0.1322865996033784</v>
       </c>
       <c r="G50">
         <v>0.5978578925213703</v>
@@ -1726,19 +1726,19 @@
         </is>
       </c>
       <c r="C51">
-        <v>3.302389936950732</v>
+        <v>3.302389936950734</v>
       </c>
       <c r="D51">
-        <v>-6.3463694993302</v>
+        <v>-6.346369499330201</v>
       </c>
       <c r="E51">
-        <v>0.9953740276587478</v>
+        <v>0.995374027658752</v>
       </c>
       <c r="F51">
-        <v>1.135513979130179</v>
+        <v>1.135513979130178</v>
       </c>
       <c r="G51">
-        <v>-0.4775260936926443</v>
+        <v>-0.4775260936926467</v>
       </c>
     </row>
     <row r="52">
@@ -1753,19 +1753,19 @@
         </is>
       </c>
       <c r="C52">
-        <v>-0.8834550506786571</v>
+        <v>-0.8834550506786562</v>
       </c>
       <c r="D52">
-        <v>0.06773091899775667</v>
+        <v>0.06773091899775707</v>
       </c>
       <c r="E52">
-        <v>0.3323768192432824</v>
+        <v>0.3323768192432822</v>
       </c>
       <c r="F52">
-        <v>-0.09609322755587253</v>
+        <v>-0.09609322755587291</v>
       </c>
       <c r="G52">
-        <v>0.1386878509030129</v>
+        <v>0.1386878509030131</v>
       </c>
     </row>
     <row r="53">
@@ -1780,19 +1780,19 @@
         </is>
       </c>
       <c r="C53">
-        <v>2.254343289437794</v>
+        <v>2.254343289437795</v>
       </c>
       <c r="D53">
-        <v>0.3641410722700475</v>
+        <v>0.3641410722700463</v>
       </c>
       <c r="E53">
-        <v>-0.5456778896426145</v>
+        <v>-0.545677889642613</v>
       </c>
       <c r="F53">
-        <v>0.1521881379426781</v>
+        <v>0.1521881379426782</v>
       </c>
       <c r="G53">
-        <v>-1.659499361106526</v>
+        <v>-1.659499361106527</v>
       </c>
     </row>
     <row r="54">
@@ -1807,19 +1807,19 @@
         </is>
       </c>
       <c r="C54">
-        <v>0.948741909958046</v>
+        <v>0.9487419099580469</v>
       </c>
       <c r="D54">
-        <v>-0.4708588431192582</v>
+        <v>-0.4708588431192589</v>
       </c>
       <c r="E54">
-        <v>-0.3726039980113013</v>
+        <v>-0.3726039980113008</v>
       </c>
       <c r="F54">
-        <v>-0.1412061651893869</v>
+        <v>-0.1412061651893864</v>
       </c>
       <c r="G54">
-        <v>-0.7643283521938962</v>
+        <v>-0.7643283521938966</v>
       </c>
     </row>
     <row r="55">
@@ -1834,19 +1834,19 @@
         </is>
       </c>
       <c r="C55">
-        <v>-3.606789957612028</v>
+        <v>-3.606789957612027</v>
       </c>
       <c r="D55">
-        <v>1.705657318067685</v>
+        <v>1.705657318067686</v>
       </c>
       <c r="E55">
-        <v>0.1956667998392309</v>
+        <v>0.1956667998392302</v>
       </c>
       <c r="F55">
-        <v>0.008614886058773323</v>
+        <v>0.008614886058772753</v>
       </c>
       <c r="G55">
-        <v>0.2992462123067559</v>
+        <v>0.2992462123067567</v>
       </c>
     </row>
     <row r="56">
@@ -1861,19 +1861,19 @@
         </is>
       </c>
       <c r="C56">
-        <v>1.444705275825487</v>
+        <v>1.444705275825488</v>
       </c>
       <c r="D56">
-        <v>0.7820045245554237</v>
+        <v>0.7820045245554249</v>
       </c>
       <c r="E56">
-        <v>0.2773115545865182</v>
+        <v>0.2773115545865183</v>
       </c>
       <c r="F56">
-        <v>0.2982819987826089</v>
+        <v>0.2982819987826084</v>
       </c>
       <c r="G56">
-        <v>0.9571977878456898</v>
+        <v>0.9571977878456897</v>
       </c>
     </row>
     <row r="57">
@@ -1888,19 +1888,19 @@
         </is>
       </c>
       <c r="C57">
-        <v>6.740938657297208</v>
+        <v>6.740938657297206</v>
       </c>
       <c r="D57">
-        <v>4.446345648425674</v>
+        <v>4.446345648425676</v>
       </c>
       <c r="E57">
-        <v>0.08119170269677721</v>
+        <v>0.08119170269677692</v>
       </c>
       <c r="F57">
-        <v>0.7418801091016155</v>
+        <v>0.7418801091016143</v>
       </c>
       <c r="G57">
-        <v>0.177455798879184</v>
+        <v>0.1774557988791837</v>
       </c>
     </row>
     <row r="58">
@@ -1915,19 +1915,19 @@
         </is>
       </c>
       <c r="C58">
-        <v>1.854759914404623</v>
+        <v>1.854759914404624</v>
       </c>
       <c r="D58">
-        <v>-2.135687334425641</v>
+        <v>-2.135687334425643</v>
       </c>
       <c r="E58">
-        <v>0.3886983308267637</v>
+        <v>0.3886983308267674</v>
       </c>
       <c r="F58">
-        <v>1.63414741888939</v>
+        <v>1.634147418889389</v>
       </c>
       <c r="G58">
-        <v>-1.744812314995847</v>
+        <v>-1.744812314995848</v>
       </c>
     </row>
     <row r="59">
@@ -1948,13 +1948,13 @@
         <v>-4.227401768752157</v>
       </c>
       <c r="E59">
-        <v>-0.1527757945100015</v>
+        <v>-0.1527757945100021</v>
       </c>
       <c r="F59">
-        <v>-0.883916879464796</v>
+        <v>-0.8839168794647942</v>
       </c>
       <c r="G59">
-        <v>-0.2938091834960792</v>
+        <v>-0.29380918349608</v>
       </c>
     </row>
     <row r="60">
@@ -1969,19 +1969,19 @@
         </is>
       </c>
       <c r="C60">
-        <v>-0.8308944919413779</v>
+        <v>-0.8308944919413772</v>
       </c>
       <c r="D60">
-        <v>0.6348582418804413</v>
+        <v>0.6348582418804418</v>
       </c>
       <c r="E60">
-        <v>0.218471977564667</v>
+        <v>0.2184719775646668</v>
       </c>
       <c r="F60">
-        <v>0.08838815944125968</v>
+        <v>0.08838815944125936</v>
       </c>
       <c r="G60">
-        <v>0.2832799207203795</v>
+        <v>0.2832799207203798</v>
       </c>
     </row>
     <row r="61">
@@ -1996,19 +1996,19 @@
         </is>
       </c>
       <c r="C61">
-        <v>-1.524573266290293</v>
+        <v>-1.524573266290292</v>
       </c>
       <c r="D61">
-        <v>1.222058413061165</v>
+        <v>1.222058413061166</v>
       </c>
       <c r="E61">
-        <v>-0.2424988684536705</v>
+        <v>-0.2424988684536702</v>
       </c>
       <c r="F61">
-        <v>0.01231647276364637</v>
+        <v>0.01231647276364642</v>
       </c>
       <c r="G61">
-        <v>0.4405136644986469</v>
+        <v>0.4405136644986467</v>
       </c>
     </row>
     <row r="62">
@@ -2023,19 +2023,19 @@
         </is>
       </c>
       <c r="C62">
-        <v>-2.06851561616172</v>
+        <v>-2.068515616161718</v>
       </c>
       <c r="D62">
-        <v>0.1960417917271316</v>
+        <v>0.1960417917271319</v>
       </c>
       <c r="E62">
-        <v>0.8616865837082822</v>
+        <v>0.8616865837082813</v>
       </c>
       <c r="F62">
-        <v>-0.322540379676223</v>
+        <v>-0.3225403796762237</v>
       </c>
       <c r="G62">
-        <v>-0.2723479366698642</v>
+        <v>-0.2723479366698637</v>
       </c>
     </row>
     <row r="63">
@@ -2050,19 +2050,19 @@
         </is>
       </c>
       <c r="C63">
-        <v>-2.315036177301397</v>
+        <v>-2.315036177301395</v>
       </c>
       <c r="D63">
         <v>-1.05994443043516</v>
       </c>
       <c r="E63">
-        <v>0.4504282412807466</v>
+        <v>0.4504282412807443</v>
       </c>
       <c r="F63">
-        <v>-1.24040202536595</v>
+        <v>-1.240402025365949</v>
       </c>
       <c r="G63">
-        <v>-0.563527207085003</v>
+        <v>-0.5635272070850019</v>
       </c>
     </row>
     <row r="64">
@@ -2080,16 +2080,16 @@
         <v>3.009047727971009</v>
       </c>
       <c r="D64">
-        <v>1.338385982031117</v>
+        <v>1.338385982031118</v>
       </c>
       <c r="E64">
-        <v>-0.2617279032597814</v>
+        <v>-0.2617279032597815</v>
       </c>
       <c r="F64">
-        <v>0.1327724632530181</v>
+        <v>0.1327724632530182</v>
       </c>
       <c r="G64">
-        <v>0.5765602225662841</v>
+        <v>0.5765602225662837</v>
       </c>
     </row>
     <row r="65">
@@ -2104,19 +2104,19 @@
         </is>
       </c>
       <c r="C65">
-        <v>-2.04031534409932</v>
+        <v>-2.040315344099318</v>
       </c>
       <c r="D65">
-        <v>-0.01253957999960139</v>
+        <v>-0.01253957999960106</v>
       </c>
       <c r="E65">
-        <v>0.1081349780209086</v>
+        <v>0.108134978020908</v>
       </c>
       <c r="F65">
-        <v>-0.4213776672901775</v>
+        <v>-0.4213776672901774</v>
       </c>
       <c r="G65">
-        <v>-0.058848898807312</v>
+        <v>-0.05884889880731168</v>
       </c>
     </row>
     <row r="66">
@@ -2131,19 +2131,19 @@
         </is>
       </c>
       <c r="C66">
-        <v>-0.3660847363433649</v>
+        <v>-0.3660847363433645</v>
       </c>
       <c r="D66">
-        <v>2.520079621119905</v>
+        <v>2.520079621119906</v>
       </c>
       <c r="E66">
-        <v>0.1716640133036538</v>
+        <v>0.1716640133036534</v>
       </c>
       <c r="F66">
-        <v>0.2123949915073344</v>
+        <v>0.2123949915073338</v>
       </c>
       <c r="G66">
-        <v>0.0349245666513251</v>
+        <v>0.03492456665132546</v>
       </c>
     </row>
     <row r="67">
@@ -2161,16 +2161,16 @@
         <v>6.615819314677881</v>
       </c>
       <c r="D67">
-        <v>2.05563887523576</v>
+        <v>2.055638875235762</v>
       </c>
       <c r="E67">
-        <v>-0.616617005692186</v>
+        <v>-0.6166170056921858</v>
       </c>
       <c r="F67">
-        <v>0.1311944039410048</v>
+        <v>0.1311944039410054</v>
       </c>
       <c r="G67">
-        <v>1.475218326994696</v>
+        <v>1.475218326994694</v>
       </c>
     </row>
     <row r="68">
@@ -2185,19 +2185,19 @@
         </is>
       </c>
       <c r="C68">
-        <v>0.8597748940592564</v>
+        <v>0.8597748940592576</v>
       </c>
       <c r="D68">
-        <v>0.4806243928207686</v>
+        <v>0.4806243928207694</v>
       </c>
       <c r="E68">
-        <v>0.29743810770244</v>
+        <v>0.2974381077024401</v>
       </c>
       <c r="F68">
-        <v>0.2726106903552297</v>
+        <v>0.2726106903552292</v>
       </c>
       <c r="G68">
-        <v>1.003583955868979</v>
+        <v>1.00358395586898</v>
       </c>
     </row>
     <row r="69">
@@ -2212,19 +2212,19 @@
         </is>
       </c>
       <c r="C69">
-        <v>3.169849151658755</v>
+        <v>3.169849151658756</v>
       </c>
       <c r="D69">
-        <v>0.6123897639668157</v>
+        <v>0.6123897639668165</v>
       </c>
       <c r="E69">
-        <v>-0.7832157937505064</v>
+        <v>-0.7832157937505106</v>
       </c>
       <c r="F69">
-        <v>-2.738918242071316</v>
+        <v>-2.738918242071313</v>
       </c>
       <c r="G69">
-        <v>-0.4217637352797999</v>
+        <v>-0.4217637352798007</v>
       </c>
     </row>
     <row r="70">
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="C70">
-        <v>-0.2981775434389571</v>
+        <v>-0.2981775434389563</v>
       </c>
       <c r="D70">
-        <v>1.310071332989671</v>
+        <v>1.310071332989672</v>
       </c>
       <c r="E70">
-        <v>-0.1896495238965762</v>
+        <v>-0.1896495238965763</v>
       </c>
       <c r="F70">
-        <v>0.02622145152827913</v>
+        <v>0.02622145152827922</v>
       </c>
       <c r="G70">
-        <v>-0.1041530118938027</v>
+        <v>-0.1041530118938026</v>
       </c>
     </row>
     <row r="71">
@@ -2266,16 +2266,16 @@
         </is>
       </c>
       <c r="C71">
-        <v>-1.830144032463206</v>
+        <v>-1.830144032463205</v>
       </c>
       <c r="D71">
-        <v>1.863157997812447</v>
+        <v>1.863157997812446</v>
       </c>
       <c r="E71">
-        <v>0.2676817847955461</v>
+        <v>0.2676817847955467</v>
       </c>
       <c r="F71">
-        <v>0.3461798905389675</v>
+        <v>0.3461798905389664</v>
       </c>
       <c r="G71">
         <v>-1.510110264007284</v>
@@ -2293,19 +2293,19 @@
         </is>
       </c>
       <c r="C72">
-        <v>-2.353214204620136</v>
+        <v>-2.353214204620134</v>
       </c>
       <c r="D72">
-        <v>-2.598079595789053</v>
+        <v>-2.598079595789054</v>
       </c>
       <c r="E72">
-        <v>-4.638576855705605</v>
+        <v>-4.638576855705602</v>
       </c>
       <c r="F72">
-        <v>-0.1250050732331893</v>
+        <v>-0.1250050732331826</v>
       </c>
       <c r="G72">
-        <v>0.7616526933667248</v>
+        <v>0.7616526933667258</v>
       </c>
     </row>
     <row r="73">
@@ -2320,19 +2320,19 @@
         </is>
       </c>
       <c r="C73">
-        <v>-0.7880876975585895</v>
+        <v>-0.788087697558588</v>
       </c>
       <c r="D73">
         <v>-3.462625500634718</v>
       </c>
       <c r="E73">
-        <v>1.384355049020748</v>
+        <v>1.384355049020747</v>
       </c>
       <c r="F73">
-        <v>-0.4106103398599735</v>
+        <v>-0.410610339859974</v>
       </c>
       <c r="G73">
-        <v>0.5270128481411651</v>
+        <v>0.5270128481411652</v>
       </c>
     </row>
     <row r="74">
@@ -2347,19 +2347,19 @@
         </is>
       </c>
       <c r="C74">
-        <v>0.60501483947416</v>
+        <v>0.6050148394741612</v>
       </c>
       <c r="D74">
-        <v>-0.3284254106897493</v>
+        <v>-0.3284254106897491</v>
       </c>
       <c r="E74">
-        <v>-1.306016505391203</v>
+        <v>-1.306016505391201</v>
       </c>
       <c r="F74">
-        <v>0.6876266136153595</v>
+        <v>0.6876266136153608</v>
       </c>
       <c r="G74">
-        <v>0.6498581525883711</v>
+        <v>0.6498581525883705</v>
       </c>
     </row>
     <row r="75">
@@ -2374,19 +2374,19 @@
         </is>
       </c>
       <c r="C75">
-        <v>-0.2327700011212816</v>
+        <v>-0.232770001121281</v>
       </c>
       <c r="D75">
         <v>1.889899286371536</v>
       </c>
       <c r="E75">
-        <v>0.07193149182407216</v>
+        <v>0.07193149182407266</v>
       </c>
       <c r="F75">
-        <v>0.4070918845263041</v>
+        <v>0.4070918845263036</v>
       </c>
       <c r="G75">
-        <v>-0.02399729492695571</v>
+        <v>-0.02399729492695592</v>
       </c>
     </row>
     <row r="76">
@@ -2401,19 +2401,19 @@
         </is>
       </c>
       <c r="C76">
-        <v>-1.834721931772492</v>
+        <v>-1.834721931772491</v>
       </c>
       <c r="D76">
         <v>1.720454267590556</v>
       </c>
       <c r="E76">
-        <v>-0.4207512057019466</v>
+        <v>-0.4207512057019475</v>
       </c>
       <c r="F76">
-        <v>-0.5404289373923952</v>
+        <v>-0.5404289373923947</v>
       </c>
       <c r="G76">
-        <v>-0.3411384269544125</v>
+        <v>-0.3411384269544124</v>
       </c>
     </row>
     <row r="77">
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="C77">
-        <v>3.98041545655807</v>
+        <v>3.980415456558069</v>
       </c>
       <c r="D77">
-        <v>3.684406435525249</v>
+        <v>3.68440643552525</v>
       </c>
       <c r="E77">
-        <v>0.1358040849495979</v>
+        <v>0.1358040849495972</v>
       </c>
       <c r="F77">
-        <v>0.3919577762717945</v>
+        <v>0.3919577762717933</v>
       </c>
       <c r="G77">
-        <v>0.2655984673995713</v>
+        <v>0.2655984673995714</v>
       </c>
     </row>
     <row r="78">
@@ -2455,19 +2455,19 @@
         </is>
       </c>
       <c r="C78">
-        <v>2.832152147615796</v>
+        <v>2.832152147615797</v>
       </c>
       <c r="D78">
         <v>0.3290351959188894</v>
       </c>
       <c r="E78">
-        <v>-0.3118534809298371</v>
+        <v>-0.3118534809298361</v>
       </c>
       <c r="F78">
         <v>0.6139052369916763</v>
       </c>
       <c r="G78">
-        <v>-0.1273931257081844</v>
+        <v>-0.1273931257081846</v>
       </c>
     </row>
     <row r="79">
@@ -2482,19 +2482,19 @@
         </is>
       </c>
       <c r="C79">
-        <v>2.366713443489346</v>
+        <v>2.366713443489347</v>
       </c>
       <c r="D79">
-        <v>-3.53916669376014</v>
+        <v>-3.539166693760143</v>
       </c>
       <c r="E79">
-        <v>0.4660240826219387</v>
+        <v>0.4660240826219443</v>
       </c>
       <c r="F79">
-        <v>1.571216002576017</v>
+        <v>1.571216002576016</v>
       </c>
       <c r="G79">
-        <v>-2.807926283081946</v>
+        <v>-2.807926283081949</v>
       </c>
     </row>
     <row r="80">
@@ -2509,19 +2509,19 @@
         </is>
       </c>
       <c r="C80">
-        <v>1.191543308875017</v>
+        <v>1.191543308875018</v>
       </c>
       <c r="D80">
         <v>2.715059929272269</v>
       </c>
       <c r="E80">
-        <v>0.2602758669021535</v>
+        <v>0.2602758669021538</v>
       </c>
       <c r="F80">
-        <v>0.2088862432909586</v>
+        <v>0.2088862432909576</v>
       </c>
       <c r="G80">
-        <v>-1.025354716603875</v>
+        <v>-1.025354716603876</v>
       </c>
     </row>
     <row r="81">
@@ -2536,19 +2536,19 @@
         </is>
       </c>
       <c r="C81">
-        <v>-2.405347495016765</v>
+        <v>-2.405347495016764</v>
       </c>
       <c r="D81">
-        <v>0.7921352213160199</v>
+        <v>0.7921352213160204</v>
       </c>
       <c r="E81">
-        <v>-0.06123376140049527</v>
+        <v>-0.06123376140049541</v>
       </c>
       <c r="F81">
-        <v>-0.02647955598653776</v>
+        <v>-0.02647955598653767</v>
       </c>
       <c r="G81">
-        <v>0.09516617296695067</v>
+        <v>0.09516617296695115</v>
       </c>
     </row>
     <row r="82">
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="C82">
-        <v>-2.139741001114609</v>
+        <v>-2.139741001114608</v>
       </c>
       <c r="D82">
-        <v>-0.9189279565954905</v>
+        <v>-0.918927956595491</v>
       </c>
       <c r="E82">
-        <v>-0.2608004938007888</v>
+        <v>-0.2608004938007903</v>
       </c>
       <c r="F82">
-        <v>-1.266688288043109</v>
+        <v>-1.266688288043108</v>
       </c>
       <c r="G82">
-        <v>-0.4078851381217866</v>
+        <v>-0.4078851381217858</v>
       </c>
     </row>
     <row r="83">
@@ -2590,19 +2590,19 @@
         </is>
       </c>
       <c r="C83">
-        <v>-0.8157651451522383</v>
+        <v>-0.8157651451522371</v>
       </c>
       <c r="D83">
-        <v>-0.09840980689201978</v>
+        <v>-0.09840980689202015</v>
       </c>
       <c r="E83">
-        <v>-0.3300687348163263</v>
+        <v>-0.3300687348163253</v>
       </c>
       <c r="F83">
-        <v>0.4336747299813581</v>
+        <v>0.4336747299813584</v>
       </c>
       <c r="G83">
-        <v>-0.309779944120545</v>
+        <v>-0.3097799441205447</v>
       </c>
     </row>
     <row r="84">
@@ -2617,19 +2617,19 @@
         </is>
       </c>
       <c r="C84">
-        <v>-2.28315548147958</v>
+        <v>-2.283155481479578</v>
       </c>
       <c r="D84">
-        <v>0.2966245524382449</v>
+        <v>0.296624552438245</v>
       </c>
       <c r="E84">
-        <v>-0.170290638425572</v>
+        <v>-0.1702906384255711</v>
       </c>
       <c r="F84">
-        <v>0.4816397976306551</v>
+        <v>0.4816397976306548</v>
       </c>
       <c r="G84">
-        <v>0.09036123640461291</v>
+        <v>0.09036123640461334</v>
       </c>
     </row>
     <row r="85">
@@ -2644,19 +2644,19 @@
         </is>
       </c>
       <c r="C85">
-        <v>0.1174069029359678</v>
+        <v>0.1174069029359688</v>
       </c>
       <c r="D85">
-        <v>0.3026570806086165</v>
+        <v>0.3026570806086166</v>
       </c>
       <c r="E85">
-        <v>0.3409011756943833</v>
+        <v>0.3409011756943846</v>
       </c>
       <c r="F85">
-        <v>0.4603891631931802</v>
+        <v>0.4603891631931795</v>
       </c>
       <c r="G85">
-        <v>-0.5166560593311399</v>
+        <v>-0.5166560593311407</v>
       </c>
     </row>
     <row r="86">
@@ -2671,19 +2671,19 @@
         </is>
       </c>
       <c r="C86">
-        <v>4.502837012490768</v>
+        <v>4.502837012490769</v>
       </c>
       <c r="D86">
-        <v>1.09820449924414</v>
+        <v>1.098204499244142</v>
       </c>
       <c r="E86">
-        <v>0.08829376015239229</v>
+        <v>0.08829376015239219</v>
       </c>
       <c r="F86">
-        <v>0.08758404278844666</v>
+        <v>0.08758404278844646</v>
       </c>
       <c r="G86">
-        <v>0.4963715863851991</v>
+        <v>0.4963715863851987</v>
       </c>
     </row>
     <row r="87">
@@ -2698,19 +2698,19 @@
         </is>
       </c>
       <c r="C87">
-        <v>-1.197691648850957</v>
+        <v>-1.197691648850955</v>
       </c>
       <c r="D87">
-        <v>-1.717327217568025</v>
+        <v>-1.717327217568027</v>
       </c>
       <c r="E87">
-        <v>0.670749394110758</v>
+        <v>0.67074939411076</v>
       </c>
       <c r="F87">
-        <v>0.5562062792742997</v>
+        <v>0.5562062792742983</v>
       </c>
       <c r="G87">
-        <v>-1.6722683908603</v>
+        <v>-1.672268390860301</v>
       </c>
     </row>
     <row r="88">
@@ -2725,19 +2725,19 @@
         </is>
       </c>
       <c r="C88">
-        <v>-0.3310289694861767</v>
+        <v>-0.3310289694861758</v>
       </c>
       <c r="D88">
-        <v>0.4584419634038771</v>
+        <v>0.4584419634038776</v>
       </c>
       <c r="E88">
-        <v>-0.2447880413820059</v>
+        <v>-0.2447880413820056</v>
       </c>
       <c r="F88">
-        <v>0.05341734271518983</v>
+        <v>0.05341734271519005</v>
       </c>
       <c r="G88">
-        <v>0.2802354538380258</v>
+        <v>0.2802354538380257</v>
       </c>
     </row>
     <row r="89">
@@ -2752,19 +2752,19 @@
         </is>
       </c>
       <c r="C89">
-        <v>-1.578887373045762</v>
+        <v>-1.578887373045761</v>
       </c>
       <c r="D89">
-        <v>-0.2418141925236318</v>
+        <v>-0.2418141925236316</v>
       </c>
       <c r="E89">
-        <v>0.2252169644153664</v>
+        <v>0.2252169644153675</v>
       </c>
       <c r="F89">
-        <v>0.5961999057826749</v>
+        <v>0.5961999057826743</v>
       </c>
       <c r="G89">
-        <v>0.1520484619668645</v>
+        <v>0.1520484619668648</v>
       </c>
     </row>
     <row r="90">
@@ -2788,10 +2788,10 @@
         <v>0.2369763514909373</v>
       </c>
       <c r="F90">
-        <v>0.1526400660652697</v>
+        <v>0.1526400660652689</v>
       </c>
       <c r="G90">
-        <v>-0.6380676645178605</v>
+        <v>-0.6380676645178602</v>
       </c>
     </row>
     <row r="91">
@@ -2806,19 +2806,19 @@
         </is>
       </c>
       <c r="C91">
-        <v>-2.112662795124199</v>
+        <v>-2.112662795124197</v>
       </c>
       <c r="D91">
-        <v>0.2460837235303677</v>
+        <v>0.2460837235303674</v>
       </c>
       <c r="E91">
-        <v>0.8418174666896373</v>
+        <v>0.8418174666896368</v>
       </c>
       <c r="F91">
-        <v>-0.2211692852146697</v>
+        <v>-0.2211692852146709</v>
       </c>
       <c r="G91">
-        <v>-0.7517230983292532</v>
+        <v>-0.7517230983292529</v>
       </c>
     </row>
     <row r="92">
@@ -2833,19 +2833,19 @@
         </is>
       </c>
       <c r="C92">
-        <v>-0.2878646883400792</v>
+        <v>-0.2878646883400784</v>
       </c>
       <c r="D92">
-        <v>2.179481672057548</v>
+        <v>2.179481672057547</v>
       </c>
       <c r="E92">
-        <v>0.2942124995315631</v>
+        <v>0.294212499531564</v>
       </c>
       <c r="F92">
-        <v>0.3787175961567718</v>
+        <v>0.3787175961567706</v>
       </c>
       <c r="G92">
-        <v>-1.948962857599203</v>
+        <v>-1.948962857599204</v>
       </c>
     </row>
     <row r="93">
@@ -2860,19 +2860,19 @@
         </is>
       </c>
       <c r="C93">
-        <v>-0.7835376196077476</v>
+        <v>-0.7835376196077467</v>
       </c>
       <c r="D93">
         <v>0.7107070078399347</v>
       </c>
       <c r="E93">
-        <v>-0.09049619978221969</v>
+        <v>-0.09049619978222072</v>
       </c>
       <c r="F93">
-        <v>-0.604801135363584</v>
+        <v>-0.6048011353635838</v>
       </c>
       <c r="G93">
-        <v>-0.434740227380594</v>
+        <v>-0.4347402273805937</v>
       </c>
     </row>
     <row r="94">
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="C94">
-        <v>3.166266949861755</v>
+        <v>3.166266949861757</v>
       </c>
       <c r="D94">
-        <v>-3.90961903823832</v>
+        <v>-3.909619038238323</v>
       </c>
       <c r="E94">
-        <v>-1.100987368509033</v>
+        <v>-1.100987368509024</v>
       </c>
       <c r="F94">
-        <v>4.403528951656377</v>
+        <v>4.403528951656376</v>
       </c>
       <c r="G94">
-        <v>-1.361481346834938</v>
+        <v>-1.361481346834939</v>
       </c>
     </row>
     <row r="95">
@@ -2914,19 +2914,19 @@
         </is>
       </c>
       <c r="C95">
-        <v>-1.332003402505065</v>
+        <v>-1.332003402505064</v>
       </c>
       <c r="D95">
         <v>-1.608321945879525</v>
       </c>
       <c r="E95">
-        <v>0.5875753171019203</v>
+        <v>0.5875753171019213</v>
       </c>
       <c r="F95">
-        <v>0.422426635056848</v>
+        <v>0.4224266350568475</v>
       </c>
       <c r="G95">
-        <v>0.1875660882351514</v>
+        <v>0.1875660882351516</v>
       </c>
     </row>
     <row r="96">
@@ -2941,19 +2941,19 @@
         </is>
       </c>
       <c r="C96">
-        <v>2.730721036289334</v>
+        <v>2.730721036289335</v>
       </c>
       <c r="D96">
-        <v>-0.8648620444462178</v>
+        <v>-0.8648620444462169</v>
       </c>
       <c r="E96">
-        <v>1.337799526659436</v>
+        <v>1.337799526659435</v>
       </c>
       <c r="F96">
-        <v>-0.6294194381837125</v>
+        <v>-0.6294194381837135</v>
       </c>
       <c r="G96">
-        <v>0.5290325074858864</v>
+        <v>0.5290325074858859</v>
       </c>
     </row>
     <row r="97">
@@ -2968,19 +2968,19 @@
         </is>
       </c>
       <c r="C97">
-        <v>-0.4501756123477123</v>
+        <v>-0.4501756123477116</v>
       </c>
       <c r="D97">
-        <v>1.065293081468445</v>
+        <v>1.065293081468446</v>
       </c>
       <c r="E97">
-        <v>0.1731637300069924</v>
+        <v>0.1731637300069921</v>
       </c>
       <c r="F97">
-        <v>-0.09219584935448741</v>
+        <v>-0.09219584935448773</v>
       </c>
       <c r="G97">
-        <v>-0.06545505152938026</v>
+        <v>-0.06545505152938019</v>
       </c>
     </row>
     <row r="98">
@@ -2995,19 +2995,19 @@
         </is>
       </c>
       <c r="C98">
-        <v>-3.101020244391789</v>
+        <v>-3.101020244391788</v>
       </c>
       <c r="D98">
-        <v>0.4269607212439353</v>
+        <v>0.4269607212439355</v>
       </c>
       <c r="E98">
-        <v>-0.597212156782049</v>
+        <v>-0.5972121567820483</v>
       </c>
       <c r="F98">
-        <v>0.1151200437114025</v>
+        <v>0.115120043711403</v>
       </c>
       <c r="G98">
-        <v>-0.03969871728206741</v>
+        <v>-0.03969871728206691</v>
       </c>
     </row>
     <row r="99">
@@ -3022,16 +3022,16 @@
         </is>
       </c>
       <c r="C99">
-        <v>-1.910273358018783</v>
+        <v>-1.910273358018782</v>
       </c>
       <c r="D99">
-        <v>0.3773409167109295</v>
+        <v>0.3773409167109298</v>
       </c>
       <c r="E99">
-        <v>0.1278219985429244</v>
+        <v>0.1278219985429251</v>
       </c>
       <c r="F99">
-        <v>0.4073285833961297</v>
+        <v>0.407328583396129</v>
       </c>
       <c r="G99">
         <v>0.2281104684679733</v>
@@ -3049,19 +3049,19 @@
         </is>
       </c>
       <c r="C100">
-        <v>-2.347115432941439</v>
+        <v>-2.347115432941438</v>
       </c>
       <c r="D100">
         <v>0.5918248150772065</v>
       </c>
       <c r="E100">
-        <v>-0.152159760238385</v>
+        <v>-0.1521597602383866</v>
       </c>
       <c r="F100">
-        <v>-0.8676176773028133</v>
+        <v>-0.8676176773028127</v>
       </c>
       <c r="G100">
-        <v>-0.4523336086288249</v>
+        <v>-0.4523336086288243</v>
       </c>
     </row>
     <row r="101">
@@ -3076,19 +3076,19 @@
         </is>
       </c>
       <c r="C101">
-        <v>-0.6389655402406392</v>
+        <v>-0.6389655402406382</v>
       </c>
       <c r="D101">
-        <v>-0.3589970171139992</v>
+        <v>-0.3589970171139988</v>
       </c>
       <c r="E101">
-        <v>-0.06868959270332442</v>
+        <v>-0.0686895927033245</v>
       </c>
       <c r="F101">
-        <v>-0.1329887301198071</v>
+        <v>-0.1329887301198067</v>
       </c>
       <c r="G101">
-        <v>0.1668059696565964</v>
+        <v>0.1668059696565967</v>
       </c>
     </row>
     <row r="102">
@@ -3103,19 +3103,19 @@
         </is>
       </c>
       <c r="C102">
-        <v>-1.019852153484278</v>
+        <v>-1.019852153484276</v>
       </c>
       <c r="D102">
-        <v>0.2993599914054055</v>
+        <v>0.299359991405406</v>
       </c>
       <c r="E102">
-        <v>0.6041127275173757</v>
+        <v>0.6041127275173752</v>
       </c>
       <c r="F102">
-        <v>-0.004324998651356933</v>
+        <v>-0.004324998651357506</v>
       </c>
       <c r="G102">
-        <v>0.05425411031753728</v>
+        <v>0.05425411031753756</v>
       </c>
     </row>
     <row r="103">
@@ -3136,13 +3136,13 @@
         <v>1.026724634806454</v>
       </c>
       <c r="E103">
-        <v>0.1966332872777586</v>
+        <v>0.1966332872777581</v>
       </c>
       <c r="F103">
-        <v>-0.149848497298101</v>
+        <v>-0.1498484972981012</v>
       </c>
       <c r="G103">
-        <v>-0.526085029828796</v>
+        <v>-0.5260850298287963</v>
       </c>
     </row>
     <row r="104">
@@ -3157,16 +3157,16 @@
         </is>
       </c>
       <c r="C104">
-        <v>0.5729780959758829</v>
+        <v>0.572978095975884</v>
       </c>
       <c r="D104">
-        <v>-0.8953073094244819</v>
+        <v>-0.895307309424481</v>
       </c>
       <c r="E104">
-        <v>0.1157216263805867</v>
+        <v>0.1157216263805879</v>
       </c>
       <c r="F104">
-        <v>0.6443535728447551</v>
+        <v>0.6443535728447549</v>
       </c>
       <c r="G104">
         <v>1.166687570048452</v>
@@ -3184,19 +3184,19 @@
         </is>
       </c>
       <c r="C105">
-        <v>4.140132524301466</v>
+        <v>4.140132524301465</v>
       </c>
       <c r="D105">
-        <v>2.369392484123732</v>
+        <v>2.369392484123733</v>
       </c>
       <c r="E105">
-        <v>0.4630374894065299</v>
+        <v>0.4630374894065292</v>
       </c>
       <c r="F105">
-        <v>0.2192618096935159</v>
+        <v>0.2192618096935151</v>
       </c>
       <c r="G105">
-        <v>0.4630677945775294</v>
+        <v>0.4630677945775293</v>
       </c>
     </row>
     <row r="106">
@@ -3211,19 +3211,19 @@
         </is>
       </c>
       <c r="C106">
-        <v>-0.3576525300405139</v>
+        <v>-0.357652530040513</v>
       </c>
       <c r="D106">
-        <v>0.6318701692683544</v>
+        <v>0.6318701692683543</v>
       </c>
       <c r="E106">
-        <v>-0.2463180741336115</v>
+        <v>-0.2463180741336117</v>
       </c>
       <c r="F106">
-        <v>-0.4994822893668995</v>
+        <v>-0.4994822893668991</v>
       </c>
       <c r="G106">
-        <v>-0.3592082209099898</v>
+        <v>-0.3592082209099904</v>
       </c>
     </row>
     <row r="107">
@@ -3241,16 +3241,16 @@
         <v>2.814075286493206</v>
       </c>
       <c r="D107">
-        <v>0.8132970007283408</v>
+        <v>0.8132970007283422</v>
       </c>
       <c r="E107">
-        <v>0.4707522761171793</v>
+        <v>0.4707522761171786</v>
       </c>
       <c r="F107">
-        <v>-0.206442576677547</v>
+        <v>-0.2064425766775475</v>
       </c>
       <c r="G107">
-        <v>0.8312000645506618</v>
+        <v>0.8312000645506615</v>
       </c>
     </row>
     <row r="108">
@@ -3265,19 +3265,19 @@
         </is>
       </c>
       <c r="C108">
-        <v>-0.9759511822889133</v>
+        <v>-0.975951182288912</v>
       </c>
       <c r="D108">
         <v>-0.2750794068269973</v>
       </c>
       <c r="E108">
-        <v>0.06774927414063214</v>
+        <v>0.06774927414063389</v>
       </c>
       <c r="F108">
-        <v>1.055001209439569</v>
+        <v>1.055001209439568</v>
       </c>
       <c r="G108">
-        <v>0.1333789298183723</v>
+        <v>0.1333789298183728</v>
       </c>
     </row>
     <row r="109">
@@ -3292,19 +3292,19 @@
         </is>
       </c>
       <c r="C109">
-        <v>0.9137073633508198</v>
+        <v>0.913707363350821</v>
       </c>
       <c r="D109">
         <v>-2.023333748768663</v>
       </c>
       <c r="E109">
-        <v>0.829944061169769</v>
+        <v>0.8299440611697697</v>
       </c>
       <c r="F109">
-        <v>0.3606397421462457</v>
+        <v>0.3606397421462448</v>
       </c>
       <c r="G109">
-        <v>0.694463816427332</v>
+        <v>0.6944638164273322</v>
       </c>
     </row>
     <row r="110">
@@ -3319,19 +3319,19 @@
         </is>
       </c>
       <c r="C110">
-        <v>-1.337299729400458</v>
+        <v>-1.337299729400457</v>
       </c>
       <c r="D110">
-        <v>0.735957232297491</v>
+        <v>0.7359572322974914</v>
       </c>
       <c r="E110">
-        <v>-0.9963601206453176</v>
+        <v>-0.9963601206453169</v>
       </c>
       <c r="F110">
-        <v>0.08527702427250379</v>
+        <v>0.08527702427250508</v>
       </c>
       <c r="G110">
-        <v>0.3575803396130525</v>
+        <v>0.3575803396130526</v>
       </c>
     </row>
     <row r="111">
@@ -3349,16 +3349,16 @@
         <v>1.596998993141129</v>
       </c>
       <c r="D111">
-        <v>3.031847502461006</v>
+        <v>3.031847502461007</v>
       </c>
       <c r="E111">
-        <v>0.204581288926252</v>
+        <v>0.2045812889262514</v>
       </c>
       <c r="F111">
-        <v>-0.06929690684777405</v>
+        <v>-0.06929690684777484</v>
       </c>
       <c r="G111">
-        <v>0.2781751733611081</v>
+        <v>0.2781751733611075</v>
       </c>
     </row>
     <row r="112">
@@ -3373,19 +3373,19 @@
         </is>
       </c>
       <c r="C112">
-        <v>-1.303983731647782</v>
+        <v>-1.30398373164778</v>
       </c>
       <c r="D112">
-        <v>-2.334287708535092</v>
+        <v>-2.334287708535093</v>
       </c>
       <c r="E112">
-        <v>-1.27249630282843</v>
+        <v>-1.272496302828429</v>
       </c>
       <c r="F112">
-        <v>-0.2924413536329896</v>
+        <v>-0.292441353632987</v>
       </c>
       <c r="G112">
-        <v>0.0004364639143437744</v>
+        <v>0.0004364639143442928</v>
       </c>
     </row>
     <row r="113">
@@ -3400,19 +3400,19 @@
         </is>
       </c>
       <c r="C113">
-        <v>2.152297056743718</v>
+        <v>2.15229705674372</v>
       </c>
       <c r="D113">
-        <v>-0.397826774593021</v>
+        <v>-0.3978267745930231</v>
       </c>
       <c r="E113">
-        <v>-6.926969086672078</v>
+        <v>-6.926969086672085</v>
       </c>
       <c r="F113">
-        <v>-5.372387549495655</v>
+        <v>-5.372387549495645</v>
       </c>
       <c r="G113">
-        <v>-0.7653606970336501</v>
+        <v>-0.7653606970336483</v>
       </c>
     </row>
     <row r="114">
@@ -3427,19 +3427,19 @@
         </is>
       </c>
       <c r="C114">
-        <v>-2.875386733691998</v>
+        <v>-2.875386733691997</v>
       </c>
       <c r="D114">
-        <v>0.8681231457885631</v>
+        <v>0.8681231457885636</v>
       </c>
       <c r="E114">
         <v>0.1355595126317633</v>
       </c>
       <c r="F114">
-        <v>0.001980417051960651</v>
+        <v>0.001980417051960531</v>
       </c>
       <c r="G114">
-        <v>0.00340552501368753</v>
+        <v>0.003405525013687842</v>
       </c>
     </row>
     <row r="115">
@@ -3454,16 +3454,16 @@
         </is>
       </c>
       <c r="C115">
-        <v>-3.097643103926671</v>
+        <v>-3.097643103926669</v>
       </c>
       <c r="D115">
-        <v>-2.066912473559477</v>
+        <v>-2.066912473559476</v>
       </c>
       <c r="E115">
-        <v>-0.629565913919807</v>
+        <v>-0.629565913919803</v>
       </c>
       <c r="F115">
-        <v>1.476450335434098</v>
+        <v>1.476450335434099</v>
       </c>
       <c r="G115">
         <v>1.188530052666579</v>
@@ -3481,16 +3481,16 @@
         </is>
       </c>
       <c r="C116">
-        <v>-1.433600577209119</v>
+        <v>-1.433600577209117</v>
       </c>
       <c r="D116">
         <v>-2.832830919767446</v>
       </c>
       <c r="E116">
-        <v>-0.4626172038704939</v>
+        <v>-0.4626172038704923</v>
       </c>
       <c r="F116">
-        <v>0.2287948880764707</v>
+        <v>0.2287948880764719</v>
       </c>
       <c r="G116">
         <v>0.4796112819347023</v>
@@ -3508,19 +3508,19 @@
         </is>
       </c>
       <c r="C117">
-        <v>2.159054526103671</v>
+        <v>2.159054526103672</v>
       </c>
       <c r="D117">
-        <v>-0.4905292099174728</v>
+        <v>-0.490529209917472</v>
       </c>
       <c r="E117">
-        <v>0.8470705709465739</v>
+        <v>0.8470705709465738</v>
       </c>
       <c r="F117">
-        <v>-0.1567607708429238</v>
+        <v>-0.1567607708429245</v>
       </c>
       <c r="G117">
-        <v>0.4402004629633007</v>
+        <v>0.4402004629633002</v>
       </c>
     </row>
     <row r="118">
@@ -3535,19 +3535,19 @@
         </is>
       </c>
       <c r="C118">
-        <v>-0.9053890677549802</v>
+        <v>-0.9053890677549787</v>
       </c>
       <c r="D118">
-        <v>-1.628295516675091</v>
+        <v>-1.62829551667509</v>
       </c>
       <c r="E118">
-        <v>1.599266768329477</v>
+        <v>1.599266768329475</v>
       </c>
       <c r="F118">
-        <v>-1.010634133852941</v>
+        <v>-1.010634133852943</v>
       </c>
       <c r="G118">
-        <v>0.09549330483287674</v>
+        <v>0.0954933048328772</v>
       </c>
     </row>
     <row r="119">
@@ -3562,19 +3562,19 @@
         </is>
       </c>
       <c r="C119">
-        <v>1.124531348967808</v>
+        <v>1.124531348967809</v>
       </c>
       <c r="D119">
-        <v>0.8720069058070732</v>
+        <v>0.8720069058070737</v>
       </c>
       <c r="E119">
-        <v>-0.6494102955736486</v>
+        <v>-0.6494102955736484</v>
       </c>
       <c r="F119">
-        <v>0.04054390513594225</v>
+        <v>0.04054390513594283</v>
       </c>
       <c r="G119">
-        <v>0.2385969809381344</v>
+        <v>0.2385969809381342</v>
       </c>
     </row>
     <row r="120">
@@ -3589,19 +3589,19 @@
         </is>
       </c>
       <c r="C120">
-        <v>-0.8520074054257857</v>
+        <v>-0.8520074054257847</v>
       </c>
       <c r="D120">
-        <v>0.1915180637911816</v>
+        <v>0.1915180637911825</v>
       </c>
       <c r="E120">
-        <v>0.9625463916821184</v>
+        <v>0.9625463916821168</v>
       </c>
       <c r="F120">
-        <v>-0.5139396320639743</v>
+        <v>-0.5139396320639752</v>
       </c>
       <c r="G120">
-        <v>0.3381168533792037</v>
+        <v>0.3381168533792042</v>
       </c>
     </row>
     <row r="121">
@@ -3616,19 +3616,19 @@
         </is>
       </c>
       <c r="C121">
-        <v>-4.221681062806856</v>
+        <v>-4.221681062806855</v>
       </c>
       <c r="D121">
-        <v>1.49822297638884</v>
+        <v>1.498222976388841</v>
       </c>
       <c r="E121">
-        <v>0.2233492211690798</v>
+        <v>0.2233492211690792</v>
       </c>
       <c r="F121">
-        <v>-0.1719314199068772</v>
+        <v>-0.1719314199068775</v>
       </c>
       <c r="G121">
-        <v>0.1490848096729617</v>
+        <v>0.1490848096729621</v>
       </c>
     </row>
     <row r="122">
@@ -3643,19 +3643,19 @@
         </is>
       </c>
       <c r="C122">
-        <v>-0.9478560712928139</v>
+        <v>-0.9478560712928132</v>
       </c>
       <c r="D122">
         <v>2.362541924373124</v>
       </c>
       <c r="E122">
-        <v>0.1982448976534981</v>
+        <v>0.1982448976534974</v>
       </c>
       <c r="F122">
-        <v>-0.01146245427226737</v>
+        <v>-0.01146245427226805</v>
       </c>
       <c r="G122">
-        <v>0.1684657539502801</v>
+        <v>0.1684657539502803</v>
       </c>
     </row>
     <row r="123">
@@ -3670,19 +3670,19 @@
         </is>
       </c>
       <c r="C123">
-        <v>3.568788403306104</v>
+        <v>3.568788403306105</v>
       </c>
       <c r="D123">
-        <v>1.459496325500101</v>
+        <v>1.459496325500103</v>
       </c>
       <c r="E123">
-        <v>0.1723767003832085</v>
+        <v>0.1723767003832081</v>
       </c>
       <c r="F123">
-        <v>-0.2105157028826678</v>
+        <v>-0.210515702882668</v>
       </c>
       <c r="G123">
-        <v>0.6879246755080546</v>
+        <v>0.6879246755080535</v>
       </c>
     </row>
     <row r="124">
@@ -3697,19 +3697,19 @@
         </is>
       </c>
       <c r="C124">
-        <v>-1.232888779435172</v>
+        <v>-1.232888779435171</v>
       </c>
       <c r="D124">
-        <v>-1.495459323682223</v>
+        <v>-1.495459323682222</v>
       </c>
       <c r="E124">
-        <v>0.2322304702538788</v>
+        <v>0.2322304702538801</v>
       </c>
       <c r="F124">
-        <v>0.5144689797629295</v>
+        <v>0.5144689797629293</v>
       </c>
       <c r="G124">
-        <v>0.9973457582955734</v>
+        <v>0.9973457582955733</v>
       </c>
     </row>
     <row r="125">
@@ -3724,19 +3724,19 @@
         </is>
       </c>
       <c r="C125">
-        <v>-2.008976180761638</v>
+        <v>-2.008976180761637</v>
       </c>
       <c r="D125">
         <v>1.071213668068509</v>
       </c>
       <c r="E125">
-        <v>0.07589629443350207</v>
+        <v>0.07589629443350243</v>
       </c>
       <c r="F125">
-        <v>0.4342790531805973</v>
+        <v>0.4342790531805968</v>
       </c>
       <c r="G125">
-        <v>0.2244550421136047</v>
+        <v>0.2244550421136054</v>
       </c>
     </row>
     <row r="126">
@@ -3751,19 +3751,19 @@
         </is>
       </c>
       <c r="C126">
-        <v>-0.5628109806276096</v>
+        <v>-0.5628109806276085</v>
       </c>
       <c r="D126">
         <v>0.2681194437829917</v>
       </c>
       <c r="E126">
-        <v>-0.1219953603759192</v>
+        <v>-0.121995360375918</v>
       </c>
       <c r="F126">
         <v>0.5640618486891554</v>
       </c>
       <c r="G126">
-        <v>-0.2174969560803442</v>
+        <v>-0.2174969560803443</v>
       </c>
     </row>
   </sheetData>
